--- a/artfynd/A 55724-2025 artfynd.xlsx
+++ b/artfynd/A 55724-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>108354872</v>
+        <v>136968601</v>
       </c>
       <c r="B2" t="n">
-        <v>101326</v>
+        <v>58005</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,49 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bäckehagen, Dlr</t>
+          <t>Bäckehagen, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>531350</v>
+        <v>531335</v>
       </c>
       <c r="R2" t="n">
-        <v>6722895</v>
+        <v>6722918</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,22 +750,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-04-22</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-04-22</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,31 +774,392 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Stina Von Post</t>
+          <t>Aron Dynesius</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Stina Von Post</t>
+          <t>Aron Dynesius</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136968601</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>136968765</v>
+      </c>
+      <c r="B3" t="n">
+        <v>8463</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bäckehagen, Bäckehagen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>531293</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6723051</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136968765</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>108354872</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bäckehagen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>531350</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6722895</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-04-22</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-04-22</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Stina Von Post</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Stina Von Post</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/108354872</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136968518</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101563</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bäckehagen, Bäckehagen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>531340</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6722908</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136968518</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55724-2025 artfynd.xlsx
+++ b/artfynd/A 55724-2025 artfynd.xlsx
@@ -1042,7 +1042,7 @@
         <v>136968518</v>
       </c>
       <c r="B5" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 55724-2025 artfynd.xlsx
+++ b/artfynd/A 55724-2025 artfynd.xlsx
@@ -1042,7 +1042,7 @@
         <v>136968518</v>
       </c>
       <c r="B5" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 55724-2025 artfynd.xlsx
+++ b/artfynd/A 55724-2025 artfynd.xlsx
@@ -1042,7 +1042,7 @@
         <v>136968518</v>
       </c>
       <c r="B5" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 55724-2025 artfynd.xlsx
+++ b/artfynd/A 55724-2025 artfynd.xlsx
@@ -1042,7 +1042,7 @@
         <v>136968518</v>
       </c>
       <c r="B5" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 55724-2025 artfynd.xlsx
+++ b/artfynd/A 55724-2025 artfynd.xlsx
@@ -1042,7 +1042,7 @@
         <v>136968518</v>
       </c>
       <c r="B5" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 55724-2025 artfynd.xlsx
+++ b/artfynd/A 55724-2025 artfynd.xlsx
@@ -1042,7 +1042,7 @@
         <v>136968518</v>
       </c>
       <c r="B5" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 55724-2025 artfynd.xlsx
+++ b/artfynd/A 55724-2025 artfynd.xlsx
@@ -1042,7 +1042,7 @@
         <v>136968518</v>
       </c>
       <c r="B5" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 55724-2025 artfynd.xlsx
+++ b/artfynd/A 55724-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136968601</v>
       </c>
       <c r="B2" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>136968518</v>
       </c>
       <c r="B5" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 55724-2025 artfynd.xlsx
+++ b/artfynd/A 55724-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136968601</v>
       </c>
       <c r="B2" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136968765</v>
       </c>
       <c r="B3" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>136968518</v>
       </c>
       <c r="B5" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 55724-2025 artfynd.xlsx
+++ b/artfynd/A 55724-2025 artfynd.xlsx
@@ -709,11 +709,7 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bäckehagen, Falun, Dlr</t>
@@ -826,11 +822,7 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bäckehagen, Bäckehagen, Dlr</t>
@@ -1068,11 +1060,7 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bäckehagen, Bäckehagen, Dlr</t>

--- a/artfynd/A 55724-2025 artfynd.xlsx
+++ b/artfynd/A 55724-2025 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>136968518</v>
       </c>
       <c r="B5" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 55724-2025 artfynd.xlsx
+++ b/artfynd/A 55724-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136968601</v>
       </c>
       <c r="B2" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>136968765</v>
       </c>
       <c r="B3" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136968518</v>
       </c>
       <c r="B5" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 55724-2025 artfynd.xlsx
+++ b/artfynd/A 55724-2025 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>136968518</v>
       </c>
       <c r="B5" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 55724-2025 artfynd.xlsx
+++ b/artfynd/A 55724-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136968601</v>
       </c>
       <c r="B2" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136968518</v>
       </c>
       <c r="B5" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 55724-2025 artfynd.xlsx
+++ b/artfynd/A 55724-2025 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>136968518</v>
       </c>
       <c r="B5" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 55724-2025 artfynd.xlsx
+++ b/artfynd/A 55724-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136968601</v>
       </c>
       <c r="B2" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136968518</v>
       </c>
       <c r="B5" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 55724-2025 artfynd.xlsx
+++ b/artfynd/A 55724-2025 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>136968518</v>
       </c>
       <c r="B5" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 55724-2025 artfynd.xlsx
+++ b/artfynd/A 55724-2025 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>136968518</v>
       </c>
       <c r="B5" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 55724-2025 artfynd.xlsx
+++ b/artfynd/A 55724-2025 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>136968518</v>
       </c>
       <c r="B5" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 55724-2025 artfynd.xlsx
+++ b/artfynd/A 55724-2025 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>136968518</v>
       </c>
       <c r="B5" t="n">
-        <v>101650</v>
+        <v>101651</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 55724-2025 artfynd.xlsx
+++ b/artfynd/A 55724-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136968601</v>
       </c>
       <c r="B2" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136968518</v>
       </c>
       <c r="B5" t="n">
-        <v>101651</v>
+        <v>101654</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
